--- a/artfynd/A 35415-2026 artfynd.xlsx
+++ b/artfynd/A 35415-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194124</v>
       </c>
       <c r="B2" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194137</v>
       </c>
       <c r="B3" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35415-2026 artfynd.xlsx
+++ b/artfynd/A 35415-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194124</v>
       </c>
       <c r="B2" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194137</v>
       </c>
       <c r="B3" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35415-2026 artfynd.xlsx
+++ b/artfynd/A 35415-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194124</v>
       </c>
       <c r="B2" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194137</v>
       </c>
       <c r="B3" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35415-2026 artfynd.xlsx
+++ b/artfynd/A 35415-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194124</v>
       </c>
       <c r="B2" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194137</v>
       </c>
       <c r="B3" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
